--- a/examples/sales_report.xlsx
+++ b/examples/sales_report.xlsx
@@ -419,39 +419,39 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
+          <t>month</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>unit_price</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>units</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>cost_per_unit</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>cost</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
           <t>revenue</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>unit_price</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>product</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>month</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>cost</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>cost_per_unit</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>units</t>
-        </is>
-      </c>
       <c r="H1" t="inlineStr">
         <is>
           <t>profit</t>
@@ -459,270 +459,270 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="n">
-        <v>4498.5</v>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>January</t>
+        </is>
       </c>
       <c r="B2" t="n">
         <v>29.99</v>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Widget A</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>January</t>
-        </is>
+      <c r="C2" t="n">
+        <v>150</v>
+      </c>
+      <c r="D2" t="n">
+        <v>15</v>
       </c>
       <c r="E2" t="n">
         <v>2250</v>
       </c>
       <c r="F2" t="n">
-        <v>15</v>
-      </c>
-      <c r="G2" t="n">
-        <v>150</v>
+        <v>4498.5</v>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Widget A</t>
+        </is>
       </c>
       <c r="H2" t="n">
         <v>2248.5</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="n">
-        <v>4249.150000000001</v>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>January</t>
+        </is>
       </c>
       <c r="B3" t="n">
         <v>49.99</v>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Widget B</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>January</t>
-        </is>
+      <c r="C3" t="n">
+        <v>85</v>
+      </c>
+      <c r="D3" t="n">
+        <v>25</v>
       </c>
       <c r="E3" t="n">
         <v>2125</v>
       </c>
       <c r="F3" t="n">
-        <v>25</v>
-      </c>
-      <c r="G3" t="n">
-        <v>85</v>
+        <v>4249.150000000001</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Widget B</t>
+        </is>
       </c>
       <c r="H3" t="n">
         <v>2124.150000000001</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="n">
-        <v>3998</v>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>January</t>
+        </is>
       </c>
       <c r="B4" t="n">
         <v>19.99</v>
       </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Widget C</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>January</t>
-        </is>
+      <c r="C4" t="n">
+        <v>200</v>
+      </c>
+      <c r="D4" t="n">
+        <v>8</v>
       </c>
       <c r="E4" t="n">
         <v>1600</v>
       </c>
       <c r="F4" t="n">
-        <v>8</v>
-      </c>
-      <c r="G4" t="n">
-        <v>200</v>
+        <v>3998</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Widget C</t>
+        </is>
       </c>
       <c r="H4" t="n">
         <v>2398</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="n">
-        <v>5248.25</v>
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>February</t>
+        </is>
       </c>
       <c r="B5" t="n">
         <v>29.99</v>
       </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Widget A</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>February</t>
-        </is>
+      <c r="C5" t="n">
+        <v>175</v>
+      </c>
+      <c r="D5" t="n">
+        <v>15</v>
       </c>
       <c r="E5" t="n">
         <v>2625</v>
       </c>
       <c r="F5" t="n">
-        <v>15</v>
-      </c>
-      <c r="G5" t="n">
-        <v>175</v>
+        <v>5248.25</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Widget A</t>
+        </is>
       </c>
       <c r="H5" t="n">
         <v>2623.25</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="n">
-        <v>4599.08</v>
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>February</t>
+        </is>
       </c>
       <c r="B6" t="n">
         <v>49.99</v>
       </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Widget B</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>February</t>
-        </is>
+      <c r="C6" t="n">
+        <v>92</v>
+      </c>
+      <c r="D6" t="n">
+        <v>25</v>
       </c>
       <c r="E6" t="n">
         <v>2300</v>
       </c>
       <c r="F6" t="n">
-        <v>25</v>
-      </c>
-      <c r="G6" t="n">
-        <v>92</v>
+        <v>4599.08</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Widget B</t>
+        </is>
       </c>
       <c r="H6" t="n">
         <v>2299.08</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="n">
-        <v>4497.75</v>
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>February</t>
+        </is>
       </c>
       <c r="B7" t="n">
         <v>19.99</v>
       </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Widget C</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>February</t>
-        </is>
+      <c r="C7" t="n">
+        <v>225</v>
+      </c>
+      <c r="D7" t="n">
+        <v>8</v>
       </c>
       <c r="E7" t="n">
         <v>1800</v>
       </c>
       <c r="F7" t="n">
-        <v>8</v>
-      </c>
-      <c r="G7" t="n">
-        <v>225</v>
+        <v>4497.75</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Widget C</t>
+        </is>
       </c>
       <c r="H7" t="n">
         <v>2697.75</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="n">
-        <v>5848.049999999999</v>
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>March</t>
+        </is>
       </c>
       <c r="B8" t="n">
         <v>29.99</v>
       </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Widget A</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>March</t>
-        </is>
+      <c r="C8" t="n">
+        <v>195</v>
+      </c>
+      <c r="D8" t="n">
+        <v>15</v>
       </c>
       <c r="E8" t="n">
         <v>2925</v>
       </c>
       <c r="F8" t="n">
-        <v>15</v>
-      </c>
-      <c r="G8" t="n">
-        <v>195</v>
+        <v>5848.049999999999</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Widget A</t>
+        </is>
       </c>
       <c r="H8" t="n">
         <v>2923.049999999999</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="n">
-        <v>5498.900000000001</v>
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>March</t>
+        </is>
       </c>
       <c r="B9" t="n">
         <v>49.99</v>
       </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Widget B</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>March</t>
-        </is>
+      <c r="C9" t="n">
+        <v>110</v>
+      </c>
+      <c r="D9" t="n">
+        <v>25</v>
       </c>
       <c r="E9" t="n">
         <v>2750</v>
       </c>
       <c r="F9" t="n">
-        <v>25</v>
-      </c>
-      <c r="G9" t="n">
-        <v>110</v>
+        <v>5498.900000000001</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Widget B</t>
+        </is>
       </c>
       <c r="H9" t="n">
         <v>2748.900000000001</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="n">
-        <v>4997.5</v>
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>March</t>
+        </is>
       </c>
       <c r="B10" t="n">
         <v>19.99</v>
       </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Widget C</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>March</t>
-        </is>
+      <c r="C10" t="n">
+        <v>250</v>
+      </c>
+      <c r="D10" t="n">
+        <v>8</v>
       </c>
       <c r="E10" t="n">
         <v>2000</v>
       </c>
       <c r="F10" t="n">
-        <v>8</v>
-      </c>
-      <c r="G10" t="n">
-        <v>250</v>
+        <v>4997.5</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Widget C</t>
+        </is>
       </c>
       <c r="H10" t="n">
         <v>2997.5</v>

--- a/examples/sales_report.xlsx
+++ b/examples/sales_report.xlsx
@@ -419,313 +419,313 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
+          <t>unit_price</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>profit</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>cost</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>revenue</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>cost_per_unit</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>units</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
           <t>month</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>unit_price</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>units</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>cost_per_unit</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>cost</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>revenue</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>product</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>profit</t>
-        </is>
-      </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" t="n">
+        <v>29.99</v>
+      </c>
+      <c r="B2" t="n">
+        <v>2248.5</v>
+      </c>
+      <c r="C2" t="n">
+        <v>2250</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Widget A</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>4498.5</v>
+      </c>
+      <c r="F2" t="n">
+        <v>15</v>
+      </c>
+      <c r="G2" t="n">
+        <v>150</v>
+      </c>
+      <c r="H2" t="inlineStr">
         <is>
           <t>January</t>
         </is>
       </c>
-      <c r="B2" t="n">
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>49.99</v>
+      </c>
+      <c r="B3" t="n">
+        <v>2124.150000000001</v>
+      </c>
+      <c r="C3" t="n">
+        <v>2125</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Widget B</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>4249.150000000001</v>
+      </c>
+      <c r="F3" t="n">
+        <v>25</v>
+      </c>
+      <c r="G3" t="n">
+        <v>85</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>January</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>19.99</v>
+      </c>
+      <c r="B4" t="n">
+        <v>2398</v>
+      </c>
+      <c r="C4" t="n">
+        <v>1600</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Widget C</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>3998</v>
+      </c>
+      <c r="F4" t="n">
+        <v>8</v>
+      </c>
+      <c r="G4" t="n">
+        <v>200</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>January</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
         <v>29.99</v>
       </c>
-      <c r="C2" t="n">
-        <v>150</v>
-      </c>
-      <c r="D2" t="n">
+      <c r="B5" t="n">
+        <v>2623.25</v>
+      </c>
+      <c r="C5" t="n">
+        <v>2625</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Widget A</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>5248.25</v>
+      </c>
+      <c r="F5" t="n">
         <v>15</v>
       </c>
-      <c r="E2" t="n">
-        <v>2250</v>
-      </c>
-      <c r="F2" t="n">
-        <v>4498.5</v>
-      </c>
-      <c r="G2" t="inlineStr">
+      <c r="G5" t="n">
+        <v>175</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>February</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>49.99</v>
+      </c>
+      <c r="B6" t="n">
+        <v>2299.08</v>
+      </c>
+      <c r="C6" t="n">
+        <v>2300</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Widget B</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>4599.08</v>
+      </c>
+      <c r="F6" t="n">
+        <v>25</v>
+      </c>
+      <c r="G6" t="n">
+        <v>92</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>February</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>19.99</v>
+      </c>
+      <c r="B7" t="n">
+        <v>2697.75</v>
+      </c>
+      <c r="C7" t="n">
+        <v>1800</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Widget C</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>4497.75</v>
+      </c>
+      <c r="F7" t="n">
+        <v>8</v>
+      </c>
+      <c r="G7" t="n">
+        <v>225</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>February</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>29.99</v>
+      </c>
+      <c r="B8" t="n">
+        <v>2923.049999999999</v>
+      </c>
+      <c r="C8" t="n">
+        <v>2925</v>
+      </c>
+      <c r="D8" t="inlineStr">
         <is>
           <t>Widget A</t>
         </is>
       </c>
-      <c r="H2" t="n">
-        <v>2248.5</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>January</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
+      <c r="E8" t="n">
+        <v>5848.049999999999</v>
+      </c>
+      <c r="F8" t="n">
+        <v>15</v>
+      </c>
+      <c r="G8" t="n">
+        <v>195</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>March</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
         <v>49.99</v>
       </c>
-      <c r="C3" t="n">
-        <v>85</v>
-      </c>
-      <c r="D3" t="n">
+      <c r="B9" t="n">
+        <v>2748.900000000001</v>
+      </c>
+      <c r="C9" t="n">
+        <v>2750</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Widget B</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>5498.900000000001</v>
+      </c>
+      <c r="F9" t="n">
         <v>25</v>
       </c>
-      <c r="E3" t="n">
-        <v>2125</v>
-      </c>
-      <c r="F3" t="n">
-        <v>4249.150000000001</v>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Widget B</t>
-        </is>
-      </c>
-      <c r="H3" t="n">
-        <v>2124.150000000001</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>January</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
+      <c r="G9" t="n">
+        <v>110</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>March</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
         <v>19.99</v>
       </c>
-      <c r="C4" t="n">
-        <v>200</v>
-      </c>
-      <c r="D4" t="n">
+      <c r="B10" t="n">
+        <v>2997.5</v>
+      </c>
+      <c r="C10" t="n">
+        <v>2000</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Widget C</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>4997.5</v>
+      </c>
+      <c r="F10" t="n">
         <v>8</v>
       </c>
-      <c r="E4" t="n">
-        <v>1600</v>
-      </c>
-      <c r="F4" t="n">
-        <v>3998</v>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Widget C</t>
-        </is>
-      </c>
-      <c r="H4" t="n">
-        <v>2398</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>February</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>29.99</v>
-      </c>
-      <c r="C5" t="n">
-        <v>175</v>
-      </c>
-      <c r="D5" t="n">
-        <v>15</v>
-      </c>
-      <c r="E5" t="n">
-        <v>2625</v>
-      </c>
-      <c r="F5" t="n">
-        <v>5248.25</v>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>Widget A</t>
-        </is>
-      </c>
-      <c r="H5" t="n">
-        <v>2623.25</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>February</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>49.99</v>
-      </c>
-      <c r="C6" t="n">
-        <v>92</v>
-      </c>
-      <c r="D6" t="n">
-        <v>25</v>
-      </c>
-      <c r="E6" t="n">
-        <v>2300</v>
-      </c>
-      <c r="F6" t="n">
-        <v>4599.08</v>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>Widget B</t>
-        </is>
-      </c>
-      <c r="H6" t="n">
-        <v>2299.08</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>February</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>19.99</v>
-      </c>
-      <c r="C7" t="n">
-        <v>225</v>
-      </c>
-      <c r="D7" t="n">
-        <v>8</v>
-      </c>
-      <c r="E7" t="n">
-        <v>1800</v>
-      </c>
-      <c r="F7" t="n">
-        <v>4497.75</v>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>Widget C</t>
-        </is>
-      </c>
-      <c r="H7" t="n">
-        <v>2697.75</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="G10" t="n">
+        <v>250</v>
+      </c>
+      <c r="H10" t="inlineStr">
         <is>
           <t>March</t>
         </is>
-      </c>
-      <c r="B8" t="n">
-        <v>29.99</v>
-      </c>
-      <c r="C8" t="n">
-        <v>195</v>
-      </c>
-      <c r="D8" t="n">
-        <v>15</v>
-      </c>
-      <c r="E8" t="n">
-        <v>2925</v>
-      </c>
-      <c r="F8" t="n">
-        <v>5848.049999999999</v>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>Widget A</t>
-        </is>
-      </c>
-      <c r="H8" t="n">
-        <v>2923.049999999999</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>March</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>49.99</v>
-      </c>
-      <c r="C9" t="n">
-        <v>110</v>
-      </c>
-      <c r="D9" t="n">
-        <v>25</v>
-      </c>
-      <c r="E9" t="n">
-        <v>2750</v>
-      </c>
-      <c r="F9" t="n">
-        <v>5498.900000000001</v>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>Widget B</t>
-        </is>
-      </c>
-      <c r="H9" t="n">
-        <v>2748.900000000001</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>March</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>19.99</v>
-      </c>
-      <c r="C10" t="n">
-        <v>250</v>
-      </c>
-      <c r="D10" t="n">
-        <v>8</v>
-      </c>
-      <c r="E10" t="n">
-        <v>2000</v>
-      </c>
-      <c r="F10" t="n">
-        <v>4997.5</v>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>Widget C</t>
-        </is>
-      </c>
-      <c r="H10" t="n">
-        <v>2997.5</v>
       </c>
     </row>
   </sheetData>

--- a/examples/sales_report.xlsx
+++ b/examples/sales_report.xlsx
@@ -419,313 +419,313 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
+          <t>cost</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>cost_per_unit</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>profit</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>month</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>revenue</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
           <t>unit_price</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>profit</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>cost</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>product</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>revenue</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>cost_per_unit</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>units</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>month</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
+        <v>2250</v>
+      </c>
+      <c r="B2" t="n">
+        <v>15</v>
+      </c>
+      <c r="C2" t="n">
+        <v>2248.5</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Widget A</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>January</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
+        <v>4498.5</v>
+      </c>
+      <c r="G2" t="n">
         <v>29.99</v>
       </c>
-      <c r="B2" t="n">
-        <v>2248.5</v>
-      </c>
-      <c r="C2" t="n">
-        <v>2250</v>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Widget A</t>
-        </is>
-      </c>
-      <c r="E2" t="n">
-        <v>4498.5</v>
-      </c>
-      <c r="F2" t="n">
-        <v>15</v>
-      </c>
-      <c r="G2" t="n">
+      <c r="H2" t="n">
         <v>150</v>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>January</t>
-        </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
+        <v>2125</v>
+      </c>
+      <c r="B3" t="n">
+        <v>25</v>
+      </c>
+      <c r="C3" t="n">
+        <v>2124.150000000001</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Widget B</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>January</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
+        <v>4249.150000000001</v>
+      </c>
+      <c r="G3" t="n">
         <v>49.99</v>
       </c>
-      <c r="B3" t="n">
-        <v>2124.150000000001</v>
-      </c>
-      <c r="C3" t="n">
-        <v>2125</v>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Widget B</t>
-        </is>
-      </c>
-      <c r="E3" t="n">
-        <v>4249.150000000001</v>
-      </c>
-      <c r="F3" t="n">
-        <v>25</v>
-      </c>
-      <c r="G3" t="n">
+      <c r="H3" t="n">
         <v>85</v>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>January</t>
-        </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
+        <v>1600</v>
+      </c>
+      <c r="B4" t="n">
+        <v>8</v>
+      </c>
+      <c r="C4" t="n">
+        <v>2398</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Widget C</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>January</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>3998</v>
+      </c>
+      <c r="G4" t="n">
         <v>19.99</v>
       </c>
-      <c r="B4" t="n">
-        <v>2398</v>
-      </c>
-      <c r="C4" t="n">
-        <v>1600</v>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Widget C</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
-        <v>3998</v>
-      </c>
-      <c r="F4" t="n">
-        <v>8</v>
-      </c>
-      <c r="G4" t="n">
+      <c r="H4" t="n">
         <v>200</v>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>January</t>
-        </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
+        <v>2625</v>
+      </c>
+      <c r="B5" t="n">
+        <v>15</v>
+      </c>
+      <c r="C5" t="n">
+        <v>2623.25</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Widget A</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>February</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>5248.25</v>
+      </c>
+      <c r="G5" t="n">
         <v>29.99</v>
       </c>
-      <c r="B5" t="n">
-        <v>2623.25</v>
-      </c>
-      <c r="C5" t="n">
-        <v>2625</v>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Widget A</t>
-        </is>
-      </c>
-      <c r="E5" t="n">
-        <v>5248.25</v>
-      </c>
-      <c r="F5" t="n">
-        <v>15</v>
-      </c>
-      <c r="G5" t="n">
+      <c r="H5" t="n">
         <v>175</v>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>February</t>
-        </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
+        <v>2300</v>
+      </c>
+      <c r="B6" t="n">
+        <v>25</v>
+      </c>
+      <c r="C6" t="n">
+        <v>2299.08</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Widget B</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>February</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>4599.08</v>
+      </c>
+      <c r="G6" t="n">
         <v>49.99</v>
       </c>
-      <c r="B6" t="n">
-        <v>2299.08</v>
-      </c>
-      <c r="C6" t="n">
-        <v>2300</v>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Widget B</t>
-        </is>
-      </c>
-      <c r="E6" t="n">
-        <v>4599.08</v>
-      </c>
-      <c r="F6" t="n">
-        <v>25</v>
-      </c>
-      <c r="G6" t="n">
+      <c r="H6" t="n">
         <v>92</v>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>February</t>
-        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
+        <v>1800</v>
+      </c>
+      <c r="B7" t="n">
+        <v>8</v>
+      </c>
+      <c r="C7" t="n">
+        <v>2697.75</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Widget C</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>February</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>4497.75</v>
+      </c>
+      <c r="G7" t="n">
         <v>19.99</v>
       </c>
-      <c r="B7" t="n">
-        <v>2697.75</v>
-      </c>
-      <c r="C7" t="n">
-        <v>1800</v>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Widget C</t>
-        </is>
-      </c>
-      <c r="E7" t="n">
-        <v>4497.75</v>
-      </c>
-      <c r="F7" t="n">
-        <v>8</v>
-      </c>
-      <c r="G7" t="n">
+      <c r="H7" t="n">
         <v>225</v>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>February</t>
-        </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
+        <v>2925</v>
+      </c>
+      <c r="B8" t="n">
+        <v>15</v>
+      </c>
+      <c r="C8" t="n">
+        <v>2923.049999999999</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Widget A</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>March</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>5848.049999999999</v>
+      </c>
+      <c r="G8" t="n">
         <v>29.99</v>
       </c>
-      <c r="B8" t="n">
-        <v>2923.049999999999</v>
-      </c>
-      <c r="C8" t="n">
-        <v>2925</v>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Widget A</t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>5848.049999999999</v>
-      </c>
-      <c r="F8" t="n">
-        <v>15</v>
-      </c>
-      <c r="G8" t="n">
+      <c r="H8" t="n">
         <v>195</v>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>March</t>
-        </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
+        <v>2750</v>
+      </c>
+      <c r="B9" t="n">
+        <v>25</v>
+      </c>
+      <c r="C9" t="n">
+        <v>2748.900000000001</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Widget B</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>March</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>5498.900000000001</v>
+      </c>
+      <c r="G9" t="n">
         <v>49.99</v>
       </c>
-      <c r="B9" t="n">
-        <v>2748.900000000001</v>
-      </c>
-      <c r="C9" t="n">
-        <v>2750</v>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Widget B</t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>5498.900000000001</v>
-      </c>
-      <c r="F9" t="n">
-        <v>25</v>
-      </c>
-      <c r="G9" t="n">
+      <c r="H9" t="n">
         <v>110</v>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>March</t>
-        </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
+        <v>2000</v>
+      </c>
+      <c r="B10" t="n">
+        <v>8</v>
+      </c>
+      <c r="C10" t="n">
+        <v>2997.5</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Widget C</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>March</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>4997.5</v>
+      </c>
+      <c r="G10" t="n">
         <v>19.99</v>
       </c>
-      <c r="B10" t="n">
-        <v>2997.5</v>
-      </c>
-      <c r="C10" t="n">
-        <v>2000</v>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Widget C</t>
-        </is>
-      </c>
-      <c r="E10" t="n">
-        <v>4997.5</v>
-      </c>
-      <c r="F10" t="n">
-        <v>8</v>
-      </c>
-      <c r="G10" t="n">
+      <c r="H10" t="n">
         <v>250</v>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>March</t>
-        </is>
       </c>
     </row>
   </sheetData>
